--- a/outputs/40478.xlsx
+++ b/outputs/40478.xlsx
@@ -309,30 +309,30 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="21.86"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="str">
-        <f aca="false">TRIM(MID(A1,FIND(" ",A1,FIND(" ",A1)+1)+1,FIND("-",A1)-FIND(" ",A1,FIND(" ",A1)+1)-1))</f>
+        <f aca="false">TRIM(IFERROR(MID(A1, FIND(" ", A1, FIND(" ", A1)+1)+1, FIND("-", A1)-FIND(" ", A1, FIND(" ", A1)+1)-1),""))</f>
         <v>Dell Vostro</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="str">
-        <f aca="false">TRIM(MID(A2,FIND(" ",A2,FIND(" ",A2)+1)+1,FIND("-",A2)-FIND(" ",A2,FIND(" ",A2)+1)-1))</f>
+        <f aca="false">TRIM(IFERROR(MID(A2, FIND(" ", A2, FIND(" ", A2)+1)+1, FIND("-", A2)-FIND(" ", A2, FIND(" ", A2)+1)-1),""))</f>
         <v>System</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="str">
-        <f aca="false">TRIM(MID(A3,FIND(" ",A3,FIND(" ",A3)+1)+1,FIND("-",A3)-FIND(" ",A3,FIND(" ",A3)+1)-1))</f>
+        <f aca="false">IF(ISNUMBER(FIND("-", A3)), TRIM(MID(A3, FIND(" ", A3, FIND(" ", A3)+1)+1, FIND("-", A3)-FIND(" ", A3, FIND(" ", A3)+1)-1)), "")</f>
         <v>Camera Server</v>
       </c>
     </row>
